--- a/mapping/servicenow_user_stories.xlsx
+++ b/mapping/servicenow_user_stories.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Epics'!$A$1:$C$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Stories'!$A$1:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Stories'!$A$1:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Field Maps'!$A$1:$N$176</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Open Items'!$A$1:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Open Items'!$A$1:$E$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -497,7 +497,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>3. Attach or link the 'Field Maps' sheet to stories MIG-05 to MIG-13. It lists every field map per import set table.</t>
+          <t>3. Attach or link the 'Field Maps' sheet to stories MIG-04 to MIG-12. It lists every field map per import set table.</t>
         </is>
       </c>
     </row>
@@ -707,6 +707,27 @@
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  logic in ServiceNow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>- Target fields, choice values and reference data (portfolios, programs, business units,</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  sites) are owned by the implementation team. If a field map's target field or value is</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  missing, raise it with the migration lead (MIG-02). Do not create it as part of the migration.</t>
         </is>
       </c>
     </row>
@@ -754,13 +775,14 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>SPM Migration - Foundation (fields, reference data, shared scripts)</t>
+          <t>SPM Migration - Load prerequisites (target readiness, load settings, shared script)</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Prepare the instance so Asana and Adaptive data can be loaded repeatably: update set,
-custom fields, reference data, choice values, load user and the shared script include.</t>
+          <t>Before any load: confirm the target fields, choices and reference data built by the
+implementation team match the load files, apply the load-safety settings, and add the shared
+script include.</t>
         </is>
       </c>
     </row>
@@ -785,7 +807,7 @@
 - Sections (COE areas) become portfolios, and plan sections become phase tasks.
 - Owners arrive as emails the pipeline resolved from names.
 - The HR tracker has no Asana status updates, so no Asana status-report map is needed.
-  If asana/05_project_status.csv ever has rows, copy MIG-13.</t>
+  If asana/05_project_status.csv ever has rows, copy MIG-12.</t>
         </is>
       </c>
     </row>
@@ -840,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -909,35 +931,33 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>SPM Migration - Foundation (fields, reference data, shared scripts)</t>
+          <t>SPM Migration - Load prerequisites (target readiness, load settings, shared script)</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Migration update set, load user and load-safety settings</t>
+          <t>Load user and load-safety settings</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>As a ServiceNow developer, I want a dedicated update set and a safe load configuration, so that every migration artefact moves dev -&gt; test -&gt; prod unchanged and loads don't trigger side effects.
+          <t>As a ServiceNow developer, I want a safe load configuration, so that migration loads don't trigger notifications or other side effects.
 STEPS
-1. Create update set "SPM Migration - Build" and make it current for all migration work.
-2. Create user migration.unassigned (active, no roles, email migration.unassigned@&lt;domain&gt;).
+1. Create user migration.unassigned (active, no roles, email migration.unassigned@&lt;domain&gt;).
    Unmatched people load as this user; the placeholder email is set in the pipeline's settings.yaml.
-3. Create system property spm.migration.pass (string, default "2"). It is used by the
-   two-pass close in MIG-10.
-4. In sub-production, turn outbound email off (glide.email.smtp.active = false) before any
+2. Create system property spm.migration.pass (string, default "2"). It is used by the
+   two-pass close in MIG-09.
+3. In sub-production, turn outbound email off (glide.email.smtp.active = false) before any
    load, or add a condition that suppresses notifications for records whose
    correlation_display is 'Asana' or 'Adaptive Work'.
-5. Only if loads will use the Import Set REST API (optional): create an integration user
+4. Only if loads will use the Import Set REST API (optional): create an integration user
    with roles import_set_loader + import_transformer and give its credentials to the
    migration team.</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>- Update set exists, and all artefacts from MIG-02 to MIG-13 are captured in it.
-- migration.unassigned exists and is active.
+          <t>- migration.unassigned exists and is active.
 - A test load in sub-prod sends no email notifications.
 - (If used) the integration user can POST to /api/now/import/&lt;table&gt; and nothing else.</t>
         </is>
@@ -959,69 +979,55 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>SPM Migration - Foundation (fields, reference data, shared scripts)</t>
+          <t>SPM Migration - Load prerequisites (target readiness, load settings, shared script)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Create and verify the custom fields the migration writes to</t>
+          <t>Target readiness check: fields, choices and reference data match the load files</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>As a ServiceNow developer, I want every target field in the transform maps to exist with the right type, so that no source data is dropped at load time.
+          <t>As a ServiceNow developer, I want to confirm that every target field, choice value and reference record the load files use already exists (the implementation team builds them), so that migrated data lands in the intended fields with valid values, and nothing is dropped or rejected.
 STEPS
-A. VERIFY the existing custom fields (from the Project and Demand Form Fields workbooks).
-   They must exist on BOTH pm_project and dmn_demand unless noted:
-   - u_business_owner     Reference -&gt; sys_user
-   - u_executive_sponsor  Reference -&gt; sys_user
-   - u_cn                 String (40). Keep as text so leading zeros survive
-   - u_funding_type       Choice: Opex required / Capex required / Accrete Acceleration funds Requested / Other
-   - u_funding_source     String (100). Consider converting to a Choice of the 19 Adaptive capital pools
-   - u_business_category  Choice (see MIG-03: the demand and project lists must be unified)
-   - u_sites              List. Record which table it references (open item D18)
-   - u_demand_type        Choice on dmn_demand only: New Application / New Project / HR
-B. CREATE the proposed fields (Demand stays out-of-box, so these go on pm_project only,
-   except the legacy fields):
-   - u_legacy_id          String (100), on TASK (inherited by project, project task, demand)
-   - u_legacy_url         URL, on TASK
-   - u_next_go_live_date  Date, pm_project
-   - u_estimate_type      Choice, pm_project (values in MIG-03)
-   - u_request_received   Date, pm_project
-   - u_request_assigned   Date, pm_project
-   - u_estimate_complete  Date, pm_project
-   - u_ready_for_delivery Date, pm_project
-   - u_project_assigned   Date, pm_project
-   - u_cost_center        Reference -&gt; cmn_cost_center, pm_project (or map to department instead, decision D11)
-   - u_risk_health        Choice (green / yellow / red), project_status
-   If the business declines a field, tell the migration team; they will remove its column
-   from the load files so the transform map has nothing to map.
-C. Add u_legacy_id and u_legacy_url to the Project, Project Task and Demand forms and list
-   views (read-only), and add the new pm_project fields to the Project form.
-D. Export sys_dictionary (name, element, internal_type, reference) for task, planned_task,
-   pm_project, pm_project_task, dmn_demand, project_status and planned_task_rel_planned_task
-   to CSV, and send it to the migration team (it feeds `validate-fields`).
-DEPENDS ON: MIG-01</t>
+Fields, choices and reference data are built by the implementation team. This story only
+checks that the migration matches them. Nothing is created here.
+1. Export sys_dictionary (name, element, internal_type, reference) for task, planned_task,
+   pm_project, pm_project_task, dmn_demand, project_status and planned_task_rel_planned_task.
+   Export sys_choice (name, element, value, label) for the same tables. Send both to the
+   migration lead, who runs `validate-fields` against them.
+2. Target fields: every target_field on the 'Field Maps' sheet must exist. Custom fields marked
+   "confirm exists" (for example u_legacy_id, u_next_go_live_date, the Nordic lifecycle dates,
+   u_cost_center, u_risk_health) are pending the implementation team. For each missing field,
+   either the implementation team adds it, or the migration lead drops that column from the
+   load files.
+3. Choice values: the load files carry STORED values, for example state integers,
+   u_funding_type, u_demand_type, u_business_category, expense_type, investment_class and size.
+   `validate-fields` lists any value that is not in sys_choice. The migration team fixes its
+   value maps to match; the choices themselves are not changed.
+4. Reference data: confirm that every portfolio, program, business unit, site and cost-center
+   name in the load files exists. Filter the distinct values in the load file against each
+   table. Gaps go to the implementation team.
+5. u_sites: record which table the list field references. The list-field script needs it.
+6. Repeat steps 1-4 in Test and in Prod before loading each instance.</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>- Every field listed in A and B exists with the stated type (check sys_dictionary).
-- No field name starts with u_u_.
-- The sys_dictionary export is delivered, and `validate-fields` reports 0 ERROR rows for missing fields.</t>
+          <t>- `validate-fields` reports 0 errors for missing fields and invalid choice values.
+- Each missing field or reference record is resolved: added by the implementation team, or
+  dropped from the load files.
+- The mock load has 0 reference or choice rejects.</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>MIG-01</t>
-        </is>
-      </c>
+      <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
@@ -1032,76 +1038,15 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>SPM Migration - Foundation (fields, reference data, shared scripts)</t>
+          <t>SPM Migration - Load prerequisites (target readiness, load settings, shared script)</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Reference data and choice values required before loading</t>
+          <t>Shared script include SPMMigrationUtil</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>As a ServiceNow developer, I want all referenced records and choice values to exist before the first load, so that reference and choice fields resolve instead of loading blank or being rejected.
-STEPS
-1. Portfolios (pm_portfolio): one per Asana HR section / COE area, plus the IT PMO
-   portfolio(s). Names must match the portfolio values in the load files exactly
-   (list in mapping/value_maps.csv -&gt; portfolio_name). Consolidation is pending decision D2.
-2. Programs (pm_program): only if decision D2 keeps programs.
-3. Business units (business_unit): BSMH, RSFH, GBS (decision D8).
-4. Sites: add Paducah and St Petersburg, or confirm Paducah -&gt; Kentucky and that
-   St Petersburg is retired (DQ14).
-5. Cost centers (cmn_cost_center) for Adaptive "Dept # for Expense" codes, if u_cost_center is kept.
-6. Choice lists:
-   - u_business_category: ONE unified list for demand and project, with snake_case stored
-     values, including human_resources (decision D1). Fix the 'urgent care' stored value
-     (DQ13) and the typos (DQ12).
-   - u_estimate_type: detailed_estimate, sat_detailed_estimate, detailed_estimate_straight_to_pm, packaging.
-   - u_risk_health: green, yellow, red.
-7. Export sys_choice (name, element, value, label) for the tables in MIG-02 and send it to
-   the migration team. The pipeline's value maps must use STORED values (state integers,
-   u_funding_type, u_demand_type, expense_type, investment_class, size).
-DEPENDS ON: MIG-02</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>- Every portfolio, business unit and site value that appears in the load files exists
-  (the mock load shows 0 reference rejects).
-- The sys_choice export is delivered, and `validate-fields` reports 0 "values not in sys_choice" errors.
-- u_business_category uses one list on both tables.</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>MIG-02</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>MIG-04</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>SPM Migration - Foundation (fields, reference data, shared scripts)</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Shared script include SPMMigrationUtil</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>As a ServiceNow developer, I want one script include for correlation, user and list lookups, so that every transform map resolves parents, projects, demands and list fields the same way.
 STEPS
@@ -1117,43 +1062,42 @@
 DEPENDS ON: MIG-01</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>- The script include is in the update set.
-- Background-script checks pass.
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>- Background-script checks pass.
 - byCorrelation queries by correlation_id only, and works for pm_project, planned_task and dmn_demand.</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>MIG-01</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>MIG-05</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MIG-04</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>SPM Migration - Asana to ServiceNow (in-flight HR projects and tasks)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Asana: import set + transform map for in-flight projects (u_imp_asana_project -&gt; pm_project)</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>As a PMO lead, I want in-flight Asana HR projects to load into pm_project, so that HR work is managed and reported in ServiceNow from go-live.
 STEPS
@@ -1176,8 +1120,8 @@
 FIELD MAPS for u_imp_asana_project (25). Source column -&gt; target field | settings
   u_correlation_id          -&gt; correlation_id | COALESCE; String
   u_correlation_display     -&gt; correlation_display
-  u_legacy_id               -&gt; u_legacy_id | field created in MIG-02
-  u_legacy_url              -&gt; u_legacy_url | field created in MIG-02
+  u_legacy_id               -&gt; u_legacy_id | confirm field exists (MIG-02)
+  u_legacy_url              -&gt; u_legacy_url | confirm field exists (MIG-02)
   u_short_description       -&gt; short_description
   u_description             -&gt; description
   u_project_manager         -&gt; project_manager | Reference sys_user; referenced value field = email; choice action = ignore
@@ -1225,56 +1169,59 @@
 - Business rules, record ownership and demand/project classification are handled upstream by
   the migration pipeline. Transform maps stay (almost) 1:1 - do not re-implement mapping
   logic in ServiceNow.
-DEPENDS ON: MIG-02, MIG-03, MIG-04</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
+- Target fields, choice values and reference data (portfolios, programs, business units,
+  sites) are owned by the implementation team. If a field map's target field or value is
+  missing, raise it with the migration lead (MIG-02). Do not create it as part of the migration.
+DEPENDS ON: MIG-02, MIG-03</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>- Loading asana/02_pm_project.csv creates one pm_project per row, and correlation_id
   starts with "ASANA:".
 - Re-loading the same file gives 0 inserts and N updates (idempotent).
 - project_manager, u_business_owner and assigned_to resolve by email; no new sys_user
   records are created. Unmatched people load as migration.unassigned or blank.
-- primary_portfolio resolves for every row whose portfolio exists (MIG-03).
+- primary_portfolio resolves for every row whose portfolio exists (MIG-02).
 - state holds stored integers; no new choice values are created.
 - start_date and end_date match the file (time_constraint = start_on_specific_date).
 - The description ends with the "--- Migrated from Asana ---" attribute block.</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F5" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>MIG-02, MIG-03, MIG-04</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>MIG-02, MIG-03</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>u_imp_asana_project</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>MIG-06</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>MIG-05</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>SPM Migration - Asana to ServiceNow (in-flight HR projects and tasks)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Asana: import set + transform map for project tasks (u_imp_asana_task -&gt; pm_project_task)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>As a project manager, I want my Asana plan (phases, milestones, tasks, subtasks) under my project in ServiceNow, so that I can keep running the in-flight project without rebuilding the plan.
 STEPS
@@ -1299,8 +1246,8 @@
 FIELD MAPS for u_imp_asana_task (17). Source column -&gt; target field | settings
   u_correlation_id           -&gt; correlation_id | COALESCE; String
   u_correlation_display      -&gt; correlation_display
-  u_legacy_id                -&gt; u_legacy_id | field created in MIG-02
-  u_legacy_url               -&gt; u_legacy_url | field created in MIG-02
+  u_legacy_id                -&gt; u_legacy_id | confirm field exists (MIG-02)
+  u_legacy_url               -&gt; u_legacy_url | confirm field exists (MIG-02)
   u_wbs_order                -&gt; wbs_order
   u_short_description        -&gt; short_description
   u_description              -&gt; description
@@ -1340,10 +1287,13 @@
 - Business rules, record ownership and demand/project classification are handled upstream by
   the migration pipeline. Transform maps stay (almost) 1:1 - do not re-implement mapping
   logic in ServiceNow.
-DEPENDS ON: MIG-05</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
+- Target fields, choice values and reference data (portfolios, programs, business units,
+  sites) are owned by the implementation team. If a field map's target field or value is
+  missing, raise it with the migration lead (MIG-02). Do not create it as part of the migration.
+DEPENDS ON: MIG-04</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>- Every task row has parent and top_task populated; 0 rows end in error for a missing parent.
 - Phase rows (Asana sections such as Project Initiation, Build, Test) appear as level-1
@@ -1354,40 +1304,40 @@
 - Re-loading gives 0 inserts.</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>MIG-05</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>MIG-04</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>u_imp_asana_task</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>MIG-07</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>MIG-06</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>SPM Migration - Asana to ServiceNow (in-flight HR projects and tasks)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Asana: import set + transform map for task dependencies (u_imp_asana_dependency)</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>As a project manager, I want Asana "blocked by" links to become ServiceNow dependencies, so that the critical path is preserved.
 STEPS
@@ -1398,7 +1348,7 @@
    - child = byCorrelation('planned_task', source.u_successor_correlation_id)
 4. Map type (fs) and lag directly.
 5. Add an onBefore script that sets ignore = true when parent or child cannot be found.
-6. Load AFTER MIG-06, then spot-check that successor dates did not move. If they did,
+6. Load AFTER MIG-05, then spot-check that successor dates did not move. If they did,
    record the project for a date review.
 FIELD MAPS for u_imp_asana_dependency (4). Source column -&gt; target field | settings
   u_predecessor_correlation_id -&gt; parent | COALESCE; Reference (scripted); script: answer = new SPMMigrationUtil().byCorrelation('planned_task', source.u_predecessor_correlation_id);
@@ -1430,62 +1380,65 @@
 - Business rules, record ownership and demand/project classification are handled upstream by
   the migration pipeline. Transform maps stay (almost) 1:1 - do not re-implement mapping
   logic in ServiceNow.
-DEPENDS ON: MIG-06</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
+- Target fields, choice values and reference data (portfolios, programs, business units,
+  sites) are owned by the implementation team. If a field map's target field or value is
+  missing, raise it with the migration lead (MIG-02). Do not create it as part of the migration.
+DEPENDS ON: MIG-05</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>- One planned_task_rel_planned_task row per file row.
 - Re-loading creates no duplicates.
 - Rows with unknown tasks are ignored and logged, not half-created.</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>MIG-06</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>MIG-05</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>u_imp_asana_dependency</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>MIG-08</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>MIG-07</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>SPM Migration - Asana to ServiceNow (in-flight HR projects and tasks)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>(Optional) Asana: import set + transform map for demands (u_imp_asana_demand -&gt; dmn_demand)</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>As a HR PMO lead, I want Asana items that the business re-classifies as demands to load as dmn_demand, so that nothing on the review list is lost.
 STEPS
 Build only if asana/01_dmn_demand.csv has rows after the classification review (today it
-has 0). Otherwise it follows the same steps and field list as MIG-09, using source table
+has 0). Otherwise it follows the same steps and field list as MIG-08, using source table
 u_imp_asana_demand and file data/load/asana/01_dmn_demand.csv. u_demand_type arrives as
 the HR stored value.
 FIELD MAPS for u_imp_asana_demand (26). Source column -&gt; target field | settings
   u_correlation_id          -&gt; correlation_id | COALESCE; String
   u_correlation_display     -&gt; correlation_display
-  u_legacy_id               -&gt; u_legacy_id | field created in MIG-02
-  u_legacy_url              -&gt; u_legacy_url | field created in MIG-02
+  u_legacy_id               -&gt; u_legacy_id | confirm field exists (MIG-02)
+  u_legacy_url              -&gt; u_legacy_url | confirm field exists (MIG-02)
   u_short_description       -&gt; short_description
   u_description             -&gt; description
   u_type                    -&gt; type | Choice; choice action = reject
@@ -1533,48 +1486,51 @@
 - Business rules, record ownership and demand/project classification are handled upstream by
   the migration pipeline. Transform maps stay (almost) 1:1 - do not re-implement mapping
   logic in ServiceNow.
-DEPENDS ON: MIG-09</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>- Same criteria as MIG-09, for Asana rows.</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
+- Target fields, choice values and reference data (portfolios, programs, business units,
+  sites) are owned by the implementation team. If a field map's target field or value is
+  missing, raise it with the migration lead (MIG-02). Do not create it as part of the migration.
+DEPENDS ON: MIG-08</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>- Same criteria as MIG-08, for Asana rows.</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>MIG-09</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>MIG-08</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>u_imp_asana_demand</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>MIG-09</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>MIG-08</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>SPM Migration - Adaptive (Clarizen) to ServiceNow (projects, tasks, demands)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Adaptive: import set + transform map for demands (u_imp_adaptive_demand -&gt; dmn_demand)</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>As a Nordic PMO lead, I want Adaptive requests that are still in intake or estimation to load as demands, so that they continue through ServiceNow demand management instead of being forced into projects.
 STEPS
@@ -1598,7 +1554,7 @@
 3. Auto Map Matching Fields, then check against the list below. Coalesce on u_correlation_id.
 4. state: the file carries stored demand states (e.g. submitted, draft). Loading directly
    into approved/completed can start approval flows. Test with 2 rows first; if a flow
-   starts, add the load condition from MIG-01 step 4 to that flow.
+   starts, add the load condition from MIG-01 step 3 to that flow.
 5. u_sites: add the list-field script (docs/05 section 4).
 6. Confirm that the demand-to-project conversion carries the custom fields (u_cn,
    u_funding_*, u_business_*, u_sites) onto the new project. That way migrated demands
@@ -1606,8 +1562,8 @@
 FIELD MAPS for u_imp_adaptive_demand (28). Source column -&gt; target field | settings
   u_correlation_id      -&gt; correlation_id | COALESCE; String
   u_correlation_display -&gt; correlation_display
-  u_legacy_id           -&gt; u_legacy_id | field created in MIG-02
-  u_legacy_url          -&gt; u_legacy_url | field created in MIG-02
+  u_legacy_id           -&gt; u_legacy_id | confirm field exists (MIG-02)
+  u_legacy_url          -&gt; u_legacy_url | confirm field exists (MIG-02)
   u_short_description   -&gt; short_description
   u_description         -&gt; description
   u_type                -&gt; type | Choice; choice action = reject
@@ -1657,13 +1613,16 @@
 - Business rules, record ownership and demand/project classification are handled upstream by
   the migration pipeline. Transform maps stay (almost) 1:1 - do not re-implement mapping
   logic in ServiceNow.
-DEPENDS ON: MIG-02, MIG-03, MIG-04</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
+- Target fields, choice values and reference data (portfolios, programs, business units,
+  sites) are owned by the implementation team. If a field map's target field or value is
+  missing, raise it with the migration lead (MIG-02). Do not create it as part of the migration.
+DEPENDS ON: MIG-02, MIG-03</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>- One dmn_demand per row. correlation_id starts with "ADAPTIVE:", and u_legacy_id holds
-  the Adaptive SYSID (if the field was created in MIG-02).
+  the Adaptive SYSID (once the implementation team has added it).
 - type = project, u_demand_type = the New Project stored value, and
   category = strategic unless the file says otherwise.
 - u_business_owner resolves by email; opened_by resolves or is migration.unassigned.
@@ -1672,46 +1631,46 @@
 - A migrated demand converts to a project with its custom fields intact.</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>MIG-02, MIG-03, MIG-04</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>MIG-02, MIG-03</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>u_imp_adaptive_demand</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>MIG-10</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>MIG-09</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>SPM Migration - Adaptive (Clarizen) to ServiceNow (projects, tasks, demands)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Adaptive: import set + transform map for projects (u_imp_adaptive_project -&gt; pm_project)</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>As a Nordic PMO lead, I want active and recently completed Adaptive projects in pm_project, with every Nordic field, so that delivery, go-live and cycle-time reporting continue in ServiceNow.
 STEPS
 1. Create the import set table u_imp_adaptive_project from data/load/adaptive/02_pm_project.csv.
 2. Create the transform map "Adaptive Project to pm_project".
-   TIP: build it like MIG-05. It has the same target and mostly the same fields, plus the
+   TIP: build it like MIG-04. It has the same target and mostly the same fields, plus the
    Adaptive-only fields: u_cn, u_funding_source, u_sites, u_cost_center,
    u_next_go_live_date, u_estimate_type, the 5 lifecycle dates, and phase.
 3. Auto Map Matching Fields, then check against the list below. Coalesce on u_correlation_id.
@@ -1725,8 +1684,8 @@
 FIELD MAPS for u_imp_adaptive_project (36). Source column -&gt; target field | settings
   u_correlation_id      -&gt; correlation_id | COALESCE; String
   u_correlation_display -&gt; correlation_display
-  u_legacy_id           -&gt; u_legacy_id | field created in MIG-02
-  u_legacy_url          -&gt; u_legacy_url | field created in MIG-02
+  u_legacy_id           -&gt; u_legacy_id | confirm field exists (MIG-02)
+  u_legacy_url          -&gt; u_legacy_url | confirm field exists (MIG-02)
   u_short_description   -&gt; short_description
   u_description         -&gt; description
   u_project_manager     -&gt; project_manager | Reference sys_user; referenced value field = email; choice action = ignore
@@ -1749,16 +1708,16 @@
   u_business_category   -&gt; u_business_category | Choice; choice action = reject
   u_sites               -&gt; u_sites | List; script: split names -&gt; sys_ids of the referenced table
   u_business_unit       -&gt; business_unit | Reference business_unit; referenced value field = name; choice action = reject (mock loads) / ignore (final)
-  u_cost_center         -&gt; u_cost_center | Reference cmn_cost_center; referenced value field = code; choice action = ignore; field created in MIG-02
+  u_cost_center         -&gt; u_cost_center | Reference cmn_cost_center; referenced value field = code; choice action = ignore; confirm field exists (MIG-02)
   u_priority            -&gt; priority | Choice; choice action = reject
   u_time_constraint     -&gt; time_constraint | Choice; choice action = reject
-  u_next_go_live_date   -&gt; u_next_go_live_date | Date; field created in MIG-02
-  u_estimate_type       -&gt; u_estimate_type | Choice; choice action = reject; field created in MIG-02
-  u_request_received    -&gt; u_request_received | Date; field created in MIG-02
-  u_request_assigned    -&gt; u_request_assigned | Date; field created in MIG-02
-  u_estimate_complete   -&gt; u_estimate_complete | Date; field created in MIG-02
-  u_ready_for_delivery  -&gt; u_ready_for_delivery | Date; field created in MIG-02
-  u_project_assigned    -&gt; u_project_assigned | Date; field created in MIG-02
+  u_next_go_live_date   -&gt; u_next_go_live_date | Date; confirm field exists (MIG-02)
+  u_estimate_type       -&gt; u_estimate_type | Choice; choice action = reject; confirm field exists (MIG-02)
+  u_request_received    -&gt; u_request_received | Date; confirm field exists (MIG-02)
+  u_request_assigned    -&gt; u_request_assigned | Date; confirm field exists (MIG-02)
+  u_estimate_complete   -&gt; u_estimate_complete | Date; confirm field exists (MIG-02)
+  u_ready_for_delivery  -&gt; u_ready_for_delivery | Date; confirm field exists (MIG-02)
+  u_project_assigned    -&gt; u_project_assigned | Date; confirm field exists (MIG-02)
   NO field map (read by scripts): u_demand_correlation_id, u_include_tasks
 CONVENTIONS FOR EVERY IMPORT SET / TRANSFORM MAP STORY
 - Load files come from the migration team: data/load/asana/*.csv and data/load/adaptive/*.csv.
@@ -1785,58 +1744,61 @@
 - Business rules, record ownership and demand/project classification are handled upstream by
   the migration pipeline. Transform maps stay (almost) 1:1 - do not re-implement mapping
   logic in ServiceNow.
-DEPENDS ON: MIG-02, MIG-03, MIG-04, MIG-09</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
+- Target fields, choice values and reference data (portfolios, programs, business units,
+  sites) are owned by the implementation team. If a field map's target field or value is
+  missing, raise it with the migration lead (MIG-02). Do not create it as part of the migration.
+DEPENDS ON: MIG-02, MIG-03, MIG-08</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>- One pm_project per row. The Adaptive SYSID shows in u_legacy_id.
 - u_cn, u_funding_type, u_funding_source, u_business_category, u_sites and the lifecycle
   dates are populated wherever the file has values.
 - Completed projects end in Closed Complete after pass 2, with no errors from
   "open child task" rules.
-- Projects whose demand_correlation_id is set are linked to the demand from MIG-09.
+- Projects whose demand_correlation_id is set are linked to the demand from MIG-08.
 - Re-loading gives 0 inserts.</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>MIG-02, MIG-03, MIG-04, MIG-09</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>MIG-02, MIG-03, MIG-08</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>u_imp_adaptive_project</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>MIG-11</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>MIG-10</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>SPM Migration - Adaptive (Clarizen) to ServiceNow (projects, tasks, demands)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Adaptive: import set + transform map for project tasks (u_imp_adaptive_task -&gt; pm_project_task)</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>As a project manager, I want my Adaptive work breakdown (tasks, milestones, hierarchy) under my ServiceNow project, so that in-flight IT projects keep their plan.
 STEPS
-Same build as MIG-06: import set table u_imp_adaptive_task from
+Same build as MIG-05: import set table u_imp_adaptive_task from
 data/load/adaptive/03_pm_project_task.csv, the same onBefore script, and coalesce on
 u_correlation_id. Adaptive has no collaborators, so there is no
 additional_assignee_list field map. Adaptive milestones already arrive with
@@ -1844,8 +1806,8 @@
 FIELD MAPS for u_imp_adaptive_task (16). Source column -&gt; target field | settings
   u_correlation_id      -&gt; correlation_id | COALESCE; String
   u_correlation_display -&gt; correlation_display
-  u_legacy_id           -&gt; u_legacy_id | field created in MIG-02
-  u_legacy_url          -&gt; u_legacy_url | field created in MIG-02
+  u_legacy_id           -&gt; u_legacy_id | confirm field exists (MIG-02)
+  u_legacy_url          -&gt; u_legacy_url | confirm field exists (MIG-02)
   u_wbs_order           -&gt; wbs_order
   u_short_description   -&gt; short_description
   u_description         -&gt; description
@@ -1884,53 +1846,56 @@
 - Business rules, record ownership and demand/project classification are handled upstream by
   the migration pipeline. Transform maps stay (almost) 1:1 - do not re-implement mapping
   logic in ServiceNow.
-DEPENDS ON: MIG-10</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>- Same criteria as MIG-06, for Adaptive rows.
+- Target fields, choice values and reference data (portfolios, programs, business units,
+  sites) are owned by the implementation team. If a field map's target field or value is
+  missing, raise it with the migration lead (MIG-02). Do not create it as part of the migration.
+DEPENDS ON: MIG-09</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>- Same criteria as MIG-05, for Adaptive rows.
 - The Adaptive parent/child hierarchy matches in the Gantt for 3 sampled projects.</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>MIG-10</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>MIG-09</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>u_imp_adaptive_task</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>MIG-12</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>MIG-11</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>SPM Migration - Adaptive (Clarizen) to ServiceNow (projects, tasks, demands)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Adaptive: import set + transform map for dependencies (u_imp_adaptive_dependency)</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>As a project manager, I want Adaptive predecessor links, including type and lag, to become ServiceNow dependencies, so that schedules keep their logic.
 STEPS
-Same build as MIG-07: import set table u_imp_adaptive_dependency from
+Same build as MIG-06: import set table u_imp_adaptive_dependency from
 data/load/adaptive/04_planned_task_rel_planned_task.csv. The type arrives as fs / ss / ff / sf,
 and lag is in days.
 FIELD MAPS for u_imp_adaptive_dependency (4). Source column -&gt; target field | settings
@@ -1963,49 +1928,52 @@
 - Business rules, record ownership and demand/project classification are handled upstream by
   the migration pipeline. Transform maps stay (almost) 1:1 - do not re-implement mapping
   logic in ServiceNow.
-DEPENDS ON: MIG-11</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>- Same criteria as MIG-07.
+- Target fields, choice values and reference data (portfolios, programs, business units,
+  sites) are owned by the implementation team. If a field map's target field or value is
+  missing, raise it with the migration lead (MIG-02). Do not create it as part of the migration.
+DEPENDS ON: MIG-10</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>- Same criteria as MIG-06.
 - Type and lag match Adaptive for 5 sampled links.</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>MIG-11</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>MIG-10</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>u_imp_adaptive_dependency</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>MIG-13</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>MIG-12</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>SPM Migration - Adaptive (Clarizen) to ServiceNow (projects, tasks, demands)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Adaptive: import set + transform map for status reports (u_imp_adaptive_status -&gt; project_status)</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>As a PMO lead, I want each project's last Adaptive health (6 indicators + update notes) as a ServiceNow status report, so that RAG reporting is continuous on day one.
 STEPS
@@ -2016,7 +1984,7 @@
 3. Map overall_health, schedule, cost, resources, scope and u_risk_health. The values are
    green / yellow / red, and the choice action is reject.
 4. Map comments (Adaptive Update Notes).
-5. Load after MIG-10.
+5. Load after MIG-09.
 FIELD MAPS for u_imp_adaptive_status (9). Source column -&gt; target field | settings
   u_project_correlation_id -&gt; project | COALESCE; Reference (scripted); script: answer = new SPMMigrationUtil().byCorrelation('pm_project', source.u_project_correlation_id);
   u_as_on                  -&gt; as_on | Date
@@ -2025,7 +1993,7 @@
   u_cost                   -&gt; cost | Choice; choice action = reject
   u_resources              -&gt; resources | Choice; choice action = reject
   u_scope                  -&gt; scope | Choice; choice action = reject
-  u_risk_health            -&gt; u_risk_health | Choice; choice action = reject; field created in MIG-02
+  u_risk_health            -&gt; u_risk_health | Choice; choice action = reject; confirm field exists (MIG-02)
   u_comments               -&gt; comments
 CONVENTIONS FOR EVERY IMPORT SET / TRANSFORM MAP STORY
 - Load files come from the migration team: data/load/asana/*.csv and data/load/adaptive/*.csv.
@@ -2052,50 +2020,53 @@
 - Business rules, record ownership and demand/project classification are handled upstream by
   the migration pipeline. Transform maps stay (almost) 1:1 - do not re-implement mapping
   logic in ServiceNow.
-DEPENDS ON: MIG-10</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
+- Target fields, choice values and reference data (portfolios, programs, business units,
+  sites) are owned by the implementation team. If a field map's target field or value is
+  missing, raise it with the migration lead (MIG-02). Do not create it as part of the migration.
+DEPENDS ON: MIG-09</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>- One status report per migrated project that had health or notes in Adaptive.
 - The Project status tab shows the RAG indicators.
 - Re-loading does not duplicate reports.</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>MIG-10</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>MIG-09</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>u_imp_adaptive_status</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>MIG-14</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MIG-13</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>SPM Migration - Test, reconcile and cut over</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Mock load 1: smoke test with hand-picked records</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>As a migration lead, I want about 10 hand-picked records per transform map loaded end to end, so that we find mapping and script defects before a full-volume load.
 STEPS
@@ -2110,10 +2081,10 @@
 3. Log every transform error and reject in the story, and fix them in the transform maps
    or report them to the migration team (mapping/value issues).
 4. Load the same files again to prove idempotency.
-DEPENDS ON: MIG-05, MIG-06, MIG-07, MIG-09, MIG-10, MIG-11, MIG-12, MIG-13</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
+DEPENDS ON: MIG-04, MIG-05, MIG-06, MIG-08, MIG-09, MIG-10, MIG-11, MIG-12</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>- 0 transform errors on the second run.
 - Re-running inserts 0 records.
@@ -2121,120 +2092,121 @@
 - The business signs off the sample records.</t>
         </is>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>MIG-05, MIG-06, MIG-07, MIG-09, MIG-10, MIG-11, MIG-12, MIG-13</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>MIG-15</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>MIG-04, MIG-05, MIG-06, MIG-08, MIG-09, MIG-10, MIG-11, MIG-12</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MIG-14</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>SPM Migration - Test, reconcile and cut over</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Full-volume mock loads, reconciliation, timing and rollback</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>As a migration lead, I want full-volume loads that reconcile and a tested rollback, so that cutover is predictable.
 STEPS
-1. Load all files in the MIG-14 order and record the duration of each load.
+1. Load all files in the MIG-13 order and record the duration of each load.
 2. Export pm_project, dmn_demand and pm_project_task with correlation_id to CSV, and hand
    them to the migration team for `reconcile`.
 3. Write a fix script that deletes the migration records by correlation_display
    (Asana / Adaptive Work). Children go first: dependencies, status reports, tasks,
    projects, then demands. Test it in sub-prod.
 4. Repeat the load once to rehearse it (mock 3).
-DEPENDS ON: MIG-14</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
+DEPENDS ON: MIG-13</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>- The reconcile report shows 0 missing and 0 unexpected records per table.
 - Load timings are documented.
 - The rollback script removes all migrated records and nothing else.</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F15" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>MIG-14</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>MIG-16</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>MIG-13</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>MIG-15</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>SPM Migration - Test, reconcile and cut over</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Production cutover</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>As a migration lead, I want the build promoted and the final data loaded into production, so that Asana and Adaptive can be frozen and decommissioned.
 STEPS
-1. Promote the update set to prod. Create the reference data (MIG-03) in prod.
+1. Promote the migration build (transform maps, script include, load settings) to prod, and
+   re-run the MIG-02 readiness check against prod.
 2. The source tools are frozen, and the migration team delivers the final files.
 3. Set Enforce mandatory fields = true and reference choice action = ignore. Load in the
-   MIG-14 order, then run pass 2.
+   MIG-13 order, then run pass 2.
 4. Run reconcile and the business spot-check. Go or no-go decision.
 5. Re-enable notifications, and keep u_legacy_url visible for hypercare.
-DEPENDS ON: MIG-15</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
+DEPENDS ON: MIG-14</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>- Production reconciles 100% against the final files.
 - The business signs off.
 - The rollback script is available but not needed.</t>
         </is>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F16" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>MIG-15</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>MIG-14</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I17"/>
+  <autoFilter ref="A1:I16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2339,7 +2311,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -2399,7 +2371,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -2451,7 +2423,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -2495,7 +2467,7 @@
       <c r="L4" s="4" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr"/>
@@ -2503,7 +2475,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2547,7 +2519,7 @@
       <c r="L5" s="4" t="inlineStr"/>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr"/>
@@ -2555,7 +2527,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -2607,7 +2579,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -2659,7 +2631,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -2719,7 +2691,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -2779,7 +2751,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -2839,7 +2811,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -2899,7 +2871,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -2963,7 +2935,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -3027,7 +2999,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -3091,7 +3063,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -3155,7 +3127,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -3219,7 +3191,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -3283,7 +3255,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -3343,7 +3315,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -3403,7 +3375,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -3463,7 +3435,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -3527,7 +3499,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -3587,7 +3559,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -3647,7 +3619,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -3703,7 +3675,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -3759,7 +3731,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -3819,7 +3791,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>MIG-08</t>
+          <t>MIG-07</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -3871,7 +3843,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -3931,7 +3903,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -3983,7 +3955,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -4027,7 +3999,7 @@
       <c r="L30" s="4" t="inlineStr"/>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr"/>
@@ -4035,7 +4007,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -4079,7 +4051,7 @@
       <c r="L31" s="4" t="inlineStr"/>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr"/>
@@ -4087,7 +4059,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -4139,7 +4111,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -4191,7 +4163,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -4255,7 +4227,7 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -4319,7 +4291,7 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -4383,7 +4355,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -4443,7 +4415,7 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -4499,7 +4471,7 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -4555,7 +4527,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -4611,7 +4583,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -4667,7 +4639,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -4719,7 +4691,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -4783,7 +4755,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -4847,7 +4819,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -4907,7 +4879,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -4967,7 +4939,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -5027,7 +4999,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -5087,7 +5059,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -5151,7 +5123,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -5211,7 +5183,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -5271,7 +5243,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -5331,7 +5303,7 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -5387,7 +5359,7 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>MIG-05</t>
+          <t>MIG-04</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -5443,7 +5415,7 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -5503,7 +5475,7 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -5555,7 +5527,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -5599,7 +5571,7 @@
       <c r="L57" s="4" t="inlineStr"/>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr"/>
@@ -5607,7 +5579,7 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -5651,7 +5623,7 @@
       <c r="L58" s="4" t="inlineStr"/>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr"/>
@@ -5659,7 +5631,7 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -5715,7 +5687,7 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -5771,7 +5743,7 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -5827,7 +5799,7 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -5879,7 +5851,7 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -5931,7 +5903,7 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -5983,7 +5955,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -6047,7 +6019,7 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -6107,7 +6079,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -6167,7 +6139,7 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -6219,7 +6191,7 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -6275,7 +6247,7 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -6331,7 +6303,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -6387,7 +6359,7 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -6443,7 +6415,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -6495,7 +6467,7 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>MIG-06</t>
+          <t>MIG-05</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -6555,7 +6527,7 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>MIG-07</t>
+          <t>MIG-06</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -6619,7 +6591,7 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>MIG-07</t>
+          <t>MIG-06</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -6683,7 +6655,7 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>MIG-07</t>
+          <t>MIG-06</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -6743,7 +6715,7 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>MIG-07</t>
+          <t>MIG-06</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -6795,7 +6767,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -6855,7 +6827,7 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -6907,7 +6879,7 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -6951,7 +6923,7 @@
       <c r="L81" s="4" t="inlineStr"/>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr"/>
@@ -6959,7 +6931,7 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -7003,7 +6975,7 @@
       <c r="L82" s="4" t="inlineStr"/>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N82" s="4" t="inlineStr"/>
@@ -7011,7 +6983,7 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -7063,7 +7035,7 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -7115,7 +7087,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -7175,7 +7147,7 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -7235,7 +7207,7 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -7295,7 +7267,7 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -7355,7 +7327,7 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -7419,7 +7391,7 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -7483,7 +7455,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -7547,7 +7519,7 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -7611,7 +7583,7 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -7675,7 +7647,7 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -7739,7 +7711,7 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -7791,7 +7763,7 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -7851,7 +7823,7 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -7903,7 +7875,7 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
@@ -7963,7 +7935,7 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -8023,7 +7995,7 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
@@ -8083,7 +8055,7 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -8147,7 +8119,7 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
@@ -8207,7 +8179,7 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -8263,7 +8235,7 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
@@ -8319,7 +8291,7 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -8379,7 +8351,7 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>MIG-09</t>
+          <t>MIG-08</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
@@ -8431,7 +8403,7 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -8491,7 +8463,7 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
@@ -8543,7 +8515,7 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -8587,7 +8559,7 @@
       <c r="L109" s="4" t="inlineStr"/>
       <c r="M109" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N109" s="4" t="inlineStr"/>
@@ -8595,7 +8567,7 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
@@ -8639,7 +8611,7 @@
       <c r="L110" s="4" t="inlineStr"/>
       <c r="M110" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N110" s="4" t="inlineStr"/>
@@ -8647,7 +8619,7 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -8699,7 +8671,7 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
@@ -8751,7 +8723,7 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -8815,7 +8787,7 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
@@ -8879,7 +8851,7 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -8943,7 +8915,7 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
@@ -9003,7 +8975,7 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -9063,7 +9035,7 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
@@ -9119,7 +9091,7 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -9175,7 +9147,7 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
@@ -9231,7 +9203,7 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -9287,7 +9259,7 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
@@ -9339,7 +9311,7 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -9403,7 +9375,7 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
@@ -9467,7 +9439,7 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -9527,7 +9499,7 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
@@ -9579,7 +9551,7 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -9639,7 +9611,7 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
@@ -9691,7 +9663,7 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -9751,7 +9723,7 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
@@ -9811,7 +9783,7 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -9871,7 +9843,7 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
@@ -9935,7 +9907,7 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -9987,7 +9959,7 @@
       <c r="L133" s="4" t="inlineStr"/>
       <c r="M133" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N133" s="4" t="inlineStr"/>
@@ -9995,7 +9967,7 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
@@ -10055,7 +10027,7 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -10115,7 +10087,7 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
@@ -10159,7 +10131,7 @@
       <c r="L136" s="4" t="inlineStr"/>
       <c r="M136" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N136" s="4" t="inlineStr">
@@ -10171,7 +10143,7 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -10219,7 +10191,7 @@
       <c r="L137" s="4" t="inlineStr"/>
       <c r="M137" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N137" s="4" t="inlineStr">
@@ -10231,7 +10203,7 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
@@ -10275,7 +10247,7 @@
       <c r="L138" s="4" t="inlineStr"/>
       <c r="M138" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N138" s="4" t="inlineStr">
@@ -10287,7 +10259,7 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -10331,7 +10303,7 @@
       <c r="L139" s="4" t="inlineStr"/>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N139" s="4" t="inlineStr">
@@ -10343,7 +10315,7 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
@@ -10387,7 +10359,7 @@
       <c r="L140" s="4" t="inlineStr"/>
       <c r="M140" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N140" s="4" t="inlineStr">
@@ -10399,7 +10371,7 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -10443,7 +10415,7 @@
       <c r="L141" s="4" t="inlineStr"/>
       <c r="M141" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N141" s="4" t="inlineStr">
@@ -10455,7 +10427,7 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
@@ -10499,7 +10471,7 @@
       <c r="L142" s="4" t="inlineStr"/>
       <c r="M142" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N142" s="4" t="inlineStr">
@@ -10511,7 +10483,7 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -10567,7 +10539,7 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>MIG-10</t>
+          <t>MIG-09</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
@@ -10623,7 +10595,7 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>MIG-11</t>
+          <t>MIG-10</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -10683,7 +10655,7 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>MIG-11</t>
+          <t>MIG-10</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
@@ -10735,7 +10707,7 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>MIG-11</t>
+          <t>MIG-10</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -10779,7 +10751,7 @@
       <c r="L147" s="4" t="inlineStr"/>
       <c r="M147" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N147" s="4" t="inlineStr"/>
@@ -10787,7 +10759,7 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>MIG-11</t>
+          <t>MIG-10</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
@@ -10831,7 +10803,7 @@
       <c r="L148" s="4" t="inlineStr"/>
       <c r="M148" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N148" s="4" t="inlineStr"/>
@@ -10839,7 +10811,7 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>MIG-11</t>
+          <t>MIG-10</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -10895,7 +10867,7 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>MIG-11</t>
+          <t>MIG-10</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
@@ -10951,7 +10923,7 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>MIG-11</t>
+          <t>MIG-10</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -11007,7 +10979,7 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>MIG-11</t>
+          <t>MIG-10</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
@@ -11059,7 +11031,7 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>MIG-11</t>
+          <t>MIG-10</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -11111,7 +11083,7 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>MIG-11</t>
+          <t>MIG-10</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
@@ -11163,7 +11135,7 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>MIG-11</t>
+          <t>MIG-10</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -11227,7 +11199,7 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>MIG-11</t>
+          <t>MIG-10</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
@@ -11287,7 +11259,7 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>MIG-11</t>
+          <t>MIG-10</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -11339,7 +11311,7 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>MIG-11</t>
+          <t>MIG-10</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
@@ -11395,7 +11367,7 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>MIG-11</t>
+          <t>MIG-10</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -11451,7 +11423,7 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>MIG-11</t>
+          <t>MIG-10</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -11507,7 +11479,7 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>MIG-11</t>
+          <t>MIG-10</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -11563,7 +11535,7 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>MIG-11</t>
+          <t>MIG-10</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
@@ -11615,7 +11587,7 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>MIG-11</t>
+          <t>MIG-10</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -11675,7 +11647,7 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>MIG-12</t>
+          <t>MIG-11</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
@@ -11739,7 +11711,7 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>MIG-12</t>
+          <t>MIG-11</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
@@ -11803,7 +11775,7 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>MIG-12</t>
+          <t>MIG-11</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -11863,7 +11835,7 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>MIG-12</t>
+          <t>MIG-11</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -11915,7 +11887,7 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>MIG-13</t>
+          <t>MIG-12</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
@@ -11979,7 +11951,7 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>MIG-13</t>
+          <t>MIG-12</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -12035,7 +12007,7 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>MIG-13</t>
+          <t>MIG-12</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
@@ -12095,7 +12067,7 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>MIG-13</t>
+          <t>MIG-12</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -12155,7 +12127,7 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>MIG-13</t>
+          <t>MIG-12</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -12215,7 +12187,7 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>MIG-13</t>
+          <t>MIG-12</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -12275,7 +12247,7 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>MIG-13</t>
+          <t>MIG-12</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
@@ -12335,7 +12307,7 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>MIG-13</t>
+          <t>MIG-12</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
@@ -12383,7 +12355,7 @@
       <c r="L175" s="4" t="inlineStr"/>
       <c r="M175" s="4" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="N175" s="4" t="inlineStr">
@@ -12395,7 +12367,7 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>MIG-13</t>
+          <t>MIG-12</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -12456,7 +12428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12604,22 +12576,22 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D17</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Cost center</t>
+          <t>Entity/Organization -&gt; Business Category</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Adaptive 'Dept # for Expense' (cost center table) and Asana Cost Center (blank) have no field on either form</t>
+          <t>Your task mapping sends Entity/Organization (BSMH, RSFH, GBS, External Partners) to u_business_category. Only RSFH exists on the category list; on current data 44 of 73 HR projects get no category and joint BSMH+RSFH projects become 'rsfh'.</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>(a) if Finance reports by cost center; else (b)</t>
+          <t>(b) Entity is an organization, not a work category - it already loads into business_unit and impacted_business_units. Add 'Human Resources' to the unified category list (D1)</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -12631,22 +12603,22 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Nordic lifecycle fields</t>
+          <t>u_sites field type</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Next Go-Live Date, Estimate Type, Request Received, Request Assigned, Estimate Complete, Ready For Delivery, Project Assigned have no ServiceNow field</t>
+          <t>u_sites is typed 'list' on the form. Does it reference a table (cmn_location or a custom Sites table) or hold choice values?</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>(a) - these drive leadership and cycle-time reporting. Built into target_mapping as u_ fields</t>
+          <t>Confirm in sys_dictionary (reference column on the u_sites entry). The transform-map script assumes (a)</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -12655,89 +12627,8 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>D13</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Risk health</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Adaptive Risk Health has no OOB project_status indicator</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>(a) - one field; keeps the 6-indicator status view</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>D17</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Entity/Organization -&gt; Business Category</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Your task mapping sends Entity/Organization (BSMH, RSFH, GBS, External Partners) to u_business_category. Only RSFH exists on the category list; on current data 44 of 73 HR projects get no category and joint BSMH+RSFH projects become 'rsfh'.</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>(b) Entity is an organization, not a work category - it already loads into business_unit and impacted_business_units. Add 'Human Resources' to the unified category list (D1)</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>D18</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>u_sites field type</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>u_sites is typed 'list' on the form. Does it reference a table (cmn_location or a custom Sites table) or hold choice values?</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Confirm in sys_dictionary (reference column on the u_sites entry). The transform-map script assumes (a)</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E10"/>
+  <autoFilter ref="A1:E7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/mapping/servicenow_user_stories.xlsx
+++ b/mapping/servicenow_user_stories.xlsx
@@ -617,7 +617,7 @@
 - PM Assigned | project_manager | People rule; N/A, TBD and blank count as no match
 - HRSP / SME / Project Lead | u_business_owner | People rule
 - Start Date / Due Date | start_date / end_date | Date rule
-- Project Status | state | Not Started -5, Started/Scoping 1, In Progress 2, Delayed 2, On Hold -3, blank -5
+- Project Status | state | Not Started -&gt; Pending; Started/Scoping -&gt; Investigating; In Progress -&gt; Work in Progress; Delayed -&gt; Work in Progress; On Hold -&gt; Pending; blank -&gt; Pending. Delayed and On Hold also add a description line 'Asana status: &lt;value&gt;'
 - Section/Column | primary_portfolio | pm_portfolio by name (the COE area)
 - Project Type | investment_class | Project -&gt; change, Annual Program -&gt; run, Project/Annual Program -&gt; change
 - Funding | expense_type / u_funding_type | CapEx -&gt; capex / Capex required; OpEx -&gt; opex / Opex required
@@ -752,7 +752,7 @@
 - % Complete | percent_complete | Number
 - Project Funding Type | u_funding_source | Direct
 - Funding Type | expense_type / u_funding_type | Capex -&gt; capex / Capex required; Opex -&gt; opex / Opex required
-- State | state | Active 2, On Hold -3
+- State | state | Active -&gt; Work in Progress; On Hold -&gt; Pending, plus description line 'Adaptive state: On Hold'
 - Customers | business_unit | business_unit by name
 - Business Category | u_business_category | Construction/Relocation -&gt; construction_relocation, Onboarding... -&gt; onboarding, Application -&gt; application, Epic -&gt; epic, GHC... -&gt; ghc, Infrastructure -&gt; infrastructure, Medical Group -&gt; medical_group, Revenue Cycle... -&gt; revenue_cycle, RSFH -&gt; rsfh, Security -&gt; security, Urgent Care -&gt; urgent care
 - (constant) | time_constraint | start_on_specific_date

--- a/mapping/servicenow_user_stories.xlsx
+++ b/mapping/servicenow_user_stories.xlsx
@@ -680,7 +680,7 @@
 - Assigned To | assigned_to | People rule
 - Collaborators | additional_assignee_list | Split on commas; people rule for each name; skip unmatched
 - Start Date / Due Date | start_date / end_date | Date rule
-- Task Status | state | Not Started -5, In Progress 2, Completed 3
+- Task Status | state | Not Started -&gt; Pending; Started/Scoping -&gt; Investigating; In Progress -&gt; Work in Progress; Delayed -&gt; Work in Progress; On Hold -&gt; Pending; Completed -&gt; Closed Complete; Cancelled -&gt; Closed Incomplete; blank -&gt; Pending. Delayed and On Hold also add a description line 'Asana status: &lt;value&gt;'
 - % Complete | percent_complete | 0.5 -&gt; 50
 - Notes | description | Then the description block
 - Task Name contains "Milestone" | milestone | true; start = end = due date
@@ -879,7 +879,7 @@
 - Project ID | top_task | pm_project where correlation_id = "ADAPTIVE:" + value
 - Parent ID | parent | Task where correlation_id = "ADAPTIVE:" + value; if Parent ID = Project ID or not found, the project
 - Manager | assigned_to | People rule
-- State | state | Draft -5, Active 2, On Hold -3, Completed 3, Cancelled 7
+- State | state | Draft -&gt; Pending; Active -&gt; Work in Progress; On Hold -&gt; Pending (plus description line 'Adaptive state: On Hold'); Completed -&gt; Closed Complete; Cancelled -&gt; Closed Incomplete
 - Start Date / Due Date | start_date / end_date | Date rule
 - Actual Start Date / Actual End Date | work_start / work_end | Date rule
 - % Complete | percent_complete | Number
